--- a/backend/data/financials_by_company/0811.HK.xlsx
+++ b/backend/data/financials_by_company/0811.HK.xlsx
@@ -702,61 +702,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-7680772.303821</v>
+        <v>-628731.903284</v>
       </c>
       <c r="C2" t="n">
-        <v>0.061597</v>
+        <v>0.004166</v>
       </c>
       <c r="D2" t="n">
-        <v>2109980229.42</v>
+        <v>1740678286.51</v>
       </c>
       <c r="E2" t="n">
-        <v>-124694258.36</v>
+        <v>-150902482.64</v>
       </c>
       <c r="F2" t="n">
-        <v>-124694258.36</v>
+        <v>-150902482.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1544856196.33</v>
+        <v>1305941469.01</v>
       </c>
       <c r="H2" t="n">
-        <v>263917965.31</v>
+        <v>261553887.42</v>
       </c>
       <c r="I2" t="n">
-        <v>7785810419.98</v>
+        <v>6633549935.15</v>
       </c>
       <c r="J2" t="n">
-        <v>1985285971.06</v>
+        <v>1589775803.87</v>
       </c>
       <c r="K2" t="n">
-        <v>1721368005.75</v>
+        <v>1328221916.45</v>
       </c>
       <c r="L2" t="n">
-        <v>217168251.44</v>
+        <v>80383936.20999999</v>
       </c>
       <c r="M2" t="n">
-        <v>12441882.61</v>
+        <v>19487842.59</v>
       </c>
       <c r="N2" t="n">
-        <v>245460218.1</v>
+        <v>109754708.81</v>
       </c>
       <c r="O2" t="n">
-        <v>1661869682.386179</v>
+        <v>1456215219.746716</v>
       </c>
       <c r="P2" t="n">
-        <v>1544856196.33</v>
+        <v>1305941469.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>10712970158.29</v>
+        <v>9023966182.57</v>
       </c>
       <c r="R2" t="n">
-        <v>14121793.86</v>
+        <v>15014527.05</v>
       </c>
       <c r="S2" t="n">
-        <v>1751630695.25</v>
+        <v>1355628438.27</v>
       </c>
       <c r="T2" t="n">
         <v>1233841000</v>
@@ -765,166 +765,168 @@
         <v>1233841000</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1544856196.33</v>
+        <v>1305941469.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1544856196.33</v>
+        <v>1305941469.01</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1544856196.33</v>
+        <v>1305941469.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>-58805477.52</v>
+        <v>2660207.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1603661673.85</v>
+        <v>1303281261.88</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1603661673.85</v>
+        <v>1303281261.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>105264449.29</v>
+        <v>5452811.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>1708926123.14</v>
+        <v>1308734073.86</v>
       </c>
       <c r="AH2" t="n">
-        <v>-42907463.86</v>
+        <v>4369008.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>-115178734.64</v>
+        <v>-225264796.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>41049521.85</v>
+        <v>44814503.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>74129212.79000001</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>180450293.29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
       <c r="AM2" t="n">
-        <v>217168251.44</v>
+        <v>80383936.20999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>15850084.05</v>
+        <v>9882930.01</v>
       </c>
       <c r="AO2" t="n">
-        <v>12441882.61</v>
+        <v>19487842.59</v>
       </c>
       <c r="AP2" t="n">
-        <v>245460218.1</v>
+        <v>109754708.81</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1435455508.43</v>
+        <v>1269837020.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>2927159738.31</v>
+        <v>2390416247.42</v>
       </c>
       <c r="AS2" t="n">
-        <v>59347568.92</v>
+        <v>52134472.48</v>
       </c>
       <c r="AT2" t="n">
-        <v>263917965.31</v>
+        <v>261553887.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>263917965.31</v>
+        <v>261553887.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>30463683.64</v>
+        <v>3793741.38</v>
       </c>
       <c r="AW2" t="n">
-        <v>949885624.59</v>
+        <v>906401857.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>681150144.87</v>
+        <v>564202090.35</v>
       </c>
       <c r="AY2" t="n">
-        <v>268735479.72</v>
+        <v>342199767.57</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14121793.86</v>
+        <v>15014527.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>4362615246.74</v>
+        <v>3660253268.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>7785810419.98</v>
+        <v>6633549935.15</v>
       </c>
       <c r="BC2" t="n">
-        <v>12148425666.72</v>
+        <v>10293803203.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>12148425666.72</v>
+        <v>10293803203.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-76785474.0425</v>
+        <v>-72017152.48999999</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2154923057.97</v>
+        <v>1929808121.65</v>
       </c>
       <c r="E3" t="n">
-        <v>-307141896.17</v>
+        <v>-288068609.96</v>
       </c>
       <c r="F3" t="n">
-        <v>-307141896.17</v>
+        <v>-288068609.96</v>
       </c>
       <c r="G3" t="n">
-        <v>1579146004.64</v>
+        <v>1396673063.27</v>
       </c>
       <c r="H3" t="n">
-        <v>266733643.91</v>
+        <v>240961673.91</v>
       </c>
       <c r="I3" t="n">
-        <v>7335035882.02</v>
+        <v>6900379983.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1847781161.8</v>
+        <v>1641739511.69</v>
       </c>
       <c r="K3" t="n">
-        <v>1581047517.89</v>
+        <v>1400777837.78</v>
       </c>
       <c r="L3" t="n">
-        <v>229255367.79</v>
+        <v>143435687.28</v>
       </c>
       <c r="M3" t="n">
-        <v>17875456.73</v>
+        <v>20978186.49</v>
       </c>
       <c r="N3" t="n">
-        <v>262917080.23</v>
+        <v>172924385.99</v>
       </c>
       <c r="O3" t="n">
-        <v>1809502426.7675</v>
+        <v>1612724520.74</v>
       </c>
       <c r="P3" t="n">
-        <v>1579146004.64</v>
+        <v>1396673063.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>10161197853.89</v>
+        <v>9340826889.870001</v>
       </c>
       <c r="R3" t="n">
-        <v>21779862.16</v>
+        <v>20480516.92</v>
       </c>
       <c r="S3" t="n">
-        <v>1604434266.72</v>
+        <v>1414676133.15</v>
       </c>
       <c r="T3" t="n">
         <v>1233841000</v>
@@ -933,168 +935,168 @@
         <v>1233841000</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1579146004.64</v>
+        <v>1396673063.27</v>
       </c>
       <c r="Y3" t="n">
-        <v>1579146004.64</v>
+        <v>1396673063.27</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1579146004.64</v>
+        <v>1396673063.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>-49204300.67</v>
+        <v>5437935.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1628350305.31</v>
+        <v>1391235128.21</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1628350305.31</v>
+        <v>1391235128.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>-65178244.15</v>
+        <v>-11435476.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1563172061.16</v>
+        <v>1379799651.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>-41601769.5</v>
+        <v>-35135302.55</v>
       </c>
       <c r="AI3" t="n">
-        <v>-250197711.7</v>
+        <v>-177735302.72</v>
       </c>
       <c r="AJ3" t="n">
-        <v>93245867.59</v>
+        <v>-5299205.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>156951844.11</v>
+        <v>183018511.23</v>
       </c>
       <c r="AL3" t="n">
-        <v>2429542.03</v>
+        <v>15996.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>229255367.79</v>
+        <v>143435687.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>15786255.71</v>
+        <v>8510512.220000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>17875456.73</v>
+        <v>20978186.49</v>
       </c>
       <c r="AP3" t="n">
-        <v>262917080.23</v>
+        <v>172924385.99</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1528350802.57</v>
+        <v>1437381855.86</v>
       </c>
       <c r="AR3" t="n">
-        <v>2826161971.87</v>
+        <v>2440446906.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>40287989.41</v>
+        <v>28783203.99</v>
       </c>
       <c r="AT3" t="n">
-        <v>266733643.91</v>
+        <v>240961673.91</v>
       </c>
       <c r="AU3" t="n">
-        <v>266733643.91</v>
+        <v>240961673.91</v>
       </c>
       <c r="AV3" t="n">
-        <v>19979888.16</v>
+        <v>14166706.34</v>
       </c>
       <c r="AW3" t="n">
-        <v>988938804.72</v>
+        <v>867137357.84</v>
       </c>
       <c r="AX3" t="n">
-        <v>702431193.99</v>
+        <v>605262538.38</v>
       </c>
       <c r="AY3" t="n">
-        <v>286507610.73</v>
+        <v>261874819.46</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21779862.16</v>
+        <v>20480516.92</v>
       </c>
       <c r="BA3" t="n">
-        <v>4354512774.44</v>
+        <v>3877828762.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>7335035882.02</v>
+        <v>6900379983.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>11689548656.46</v>
+        <v>10778208745.73</v>
       </c>
       <c r="BD3" t="n">
-        <v>11689548656.46</v>
+        <v>10778208745.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-72017152.48999999</v>
+        <v>-76785474.0425</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1929808121.65</v>
+        <v>2154923057.97</v>
       </c>
       <c r="E4" t="n">
-        <v>-288068609.96</v>
+        <v>-307141896.17</v>
       </c>
       <c r="F4" t="n">
-        <v>-288068609.96</v>
+        <v>-307141896.17</v>
       </c>
       <c r="G4" t="n">
-        <v>1396673063.27</v>
+        <v>1579146004.64</v>
       </c>
       <c r="H4" t="n">
-        <v>240961673.91</v>
+        <v>266733643.91</v>
       </c>
       <c r="I4" t="n">
-        <v>6900379983.7</v>
+        <v>7335035882.02</v>
       </c>
       <c r="J4" t="n">
-        <v>1641739511.69</v>
+        <v>1847781161.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1400777837.78</v>
+        <v>1581047517.89</v>
       </c>
       <c r="L4" t="n">
-        <v>143435687.28</v>
+        <v>229255367.79</v>
       </c>
       <c r="M4" t="n">
-        <v>20978186.49</v>
+        <v>17875456.73</v>
       </c>
       <c r="N4" t="n">
-        <v>172924385.99</v>
+        <v>262917080.23</v>
       </c>
       <c r="O4" t="n">
-        <v>1612724520.74</v>
+        <v>1809502426.7675</v>
       </c>
       <c r="P4" t="n">
-        <v>1396673063.27</v>
+        <v>1579146004.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>9340826889.870001</v>
+        <v>10161197853.89</v>
       </c>
       <c r="R4" t="n">
-        <v>20480516.92</v>
+        <v>21779862.16</v>
       </c>
       <c r="S4" t="n">
-        <v>1414676133.15</v>
+        <v>1604434266.72</v>
       </c>
       <c r="T4" t="n">
         <v>1233841000</v>
@@ -1103,168 +1105,168 @@
         <v>1233841000</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>1396673063.27</v>
+        <v>1579146004.64</v>
       </c>
       <c r="Y4" t="n">
-        <v>1396673063.27</v>
+        <v>1579146004.64</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1396673063.27</v>
+        <v>1579146004.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>5437935.06</v>
+        <v>-49204300.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>1391235128.21</v>
+        <v>1628350305.31</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1391235128.21</v>
+        <v>1628350305.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>-11435476.92</v>
+        <v>-65178244.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1379799651.29</v>
+        <v>1563172061.16</v>
       </c>
       <c r="AH4" t="n">
-        <v>-35135302.55</v>
+        <v>-41601769.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>-177735302.72</v>
+        <v>-250197711.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-5299205.03</v>
+        <v>93245867.59</v>
       </c>
       <c r="AK4" t="n">
-        <v>183018511.23</v>
+        <v>156951844.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>15996.52</v>
+        <v>2429542.03</v>
       </c>
       <c r="AM4" t="n">
-        <v>143435687.28</v>
+        <v>229255367.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>8510512.220000001</v>
+        <v>15786255.71</v>
       </c>
       <c r="AO4" t="n">
-        <v>20978186.49</v>
+        <v>17875456.73</v>
       </c>
       <c r="AP4" t="n">
-        <v>172924385.99</v>
+        <v>262917080.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1437381855.86</v>
+        <v>1528350802.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>2440446906.17</v>
+        <v>2826161971.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>28783203.99</v>
+        <v>40287989.41</v>
       </c>
       <c r="AT4" t="n">
-        <v>240961673.91</v>
+        <v>266733643.91</v>
       </c>
       <c r="AU4" t="n">
-        <v>240961673.91</v>
+        <v>266733643.91</v>
       </c>
       <c r="AV4" t="n">
-        <v>14166706.34</v>
+        <v>19979888.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>867137357.84</v>
+        <v>988938804.72</v>
       </c>
       <c r="AX4" t="n">
-        <v>605262538.38</v>
+        <v>702431193.99</v>
       </c>
       <c r="AY4" t="n">
-        <v>261874819.46</v>
+        <v>286507610.73</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20480516.92</v>
+        <v>21779862.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>3877828762.03</v>
+        <v>4354512774.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>6900379983.7</v>
+        <v>7335035882.02</v>
       </c>
       <c r="BC4" t="n">
-        <v>10778208745.73</v>
+        <v>11689548656.46</v>
       </c>
       <c r="BD4" t="n">
-        <v>10778208745.73</v>
+        <v>11689548656.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-628731.903284</v>
+        <v>-7680772.303821</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004166</v>
+        <v>0.061597</v>
       </c>
       <c r="D5" t="n">
-        <v>1740678286.51</v>
+        <v>2109980229.42</v>
       </c>
       <c r="E5" t="n">
-        <v>-150902482.64</v>
+        <v>-124694258.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-150902482.64</v>
+        <v>-124694258.36</v>
       </c>
       <c r="G5" t="n">
-        <v>1305941469.01</v>
+        <v>1544856196.33</v>
       </c>
       <c r="H5" t="n">
-        <v>261553887.42</v>
+        <v>263917965.31</v>
       </c>
       <c r="I5" t="n">
-        <v>6633549935.15</v>
+        <v>7785810419.98</v>
       </c>
       <c r="J5" t="n">
-        <v>1589775803.87</v>
+        <v>1985285971.06</v>
       </c>
       <c r="K5" t="n">
-        <v>1328221916.45</v>
+        <v>1721368005.75</v>
       </c>
       <c r="L5" t="n">
-        <v>80383936.20999999</v>
+        <v>217168251.44</v>
       </c>
       <c r="M5" t="n">
-        <v>19487842.59</v>
+        <v>12441882.61</v>
       </c>
       <c r="N5" t="n">
-        <v>109754708.81</v>
+        <v>245460218.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1456215219.746716</v>
+        <v>1661869682.386179</v>
       </c>
       <c r="P5" t="n">
-        <v>1305941469.01</v>
+        <v>1544856196.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>9023966182.57</v>
+        <v>10712970158.29</v>
       </c>
       <c r="R5" t="n">
-        <v>15014527.05</v>
+        <v>14121793.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1355628438.27</v>
+        <v>1751630695.25</v>
       </c>
       <c r="T5" t="n">
         <v>1233841000</v>
@@ -1273,109 +1275,107 @@
         <v>1233841000</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>1305941469.01</v>
+        <v>1544856196.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>1305941469.01</v>
+        <v>1544856196.33</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1305941469.01</v>
+        <v>1544856196.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>2660207.13</v>
+        <v>-58805477.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>1303281261.88</v>
+        <v>1603661673.85</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1303281261.88</v>
+        <v>1603661673.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>5452811.98</v>
+        <v>105264449.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>1308734073.86</v>
+        <v>1708926123.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>4369008.12</v>
+        <v>-42907463.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>-225264796.44</v>
+        <v>-115178734.64</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44814503.15</v>
+        <v>41049521.85</v>
       </c>
       <c r="AK5" t="n">
-        <v>180450293.29</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>74129212.79000001</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>80383936.20999999</v>
+        <v>217168251.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>9882930.01</v>
+        <v>15850084.05</v>
       </c>
       <c r="AO5" t="n">
-        <v>19487842.59</v>
+        <v>12441882.61</v>
       </c>
       <c r="AP5" t="n">
-        <v>109754708.81</v>
+        <v>245460218.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1269837020.73</v>
+        <v>1435455508.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>2390416247.42</v>
+        <v>2927159738.31</v>
       </c>
       <c r="AS5" t="n">
-        <v>52134472.48</v>
+        <v>59347568.92</v>
       </c>
       <c r="AT5" t="n">
-        <v>261553887.42</v>
+        <v>263917965.31</v>
       </c>
       <c r="AU5" t="n">
-        <v>261553887.42</v>
+        <v>263917965.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>3793741.38</v>
+        <v>30463683.64</v>
       </c>
       <c r="AW5" t="n">
-        <v>906401857.92</v>
+        <v>949885624.59</v>
       </c>
       <c r="AX5" t="n">
-        <v>564202090.35</v>
+        <v>681150144.87</v>
       </c>
       <c r="AY5" t="n">
-        <v>342199767.57</v>
+        <v>268735479.72</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15014527.05</v>
+        <v>14121793.86</v>
       </c>
       <c r="BA5" t="n">
-        <v>3660253268.15</v>
+        <v>4362615246.74</v>
       </c>
       <c r="BB5" t="n">
-        <v>6633549935.15</v>
+        <v>7785810419.98</v>
       </c>
       <c r="BC5" t="n">
-        <v>10293803203.3</v>
+        <v>12148425666.72</v>
       </c>
       <c r="BD5" t="n">
-        <v>10293803203.3</v>
+        <v>12148425666.72</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1233841000</v>
@@ -1790,42 +1790,44 @@
         <v>1233841000</v>
       </c>
       <c r="D2" t="n">
-        <v>271288163.86</v>
+        <v>406586133.53</v>
       </c>
       <c r="E2" t="n">
-        <v>13602953149.6</v>
+        <v>10274552734.64</v>
       </c>
       <c r="F2" t="n">
-        <v>14620942286.52</v>
+        <v>11266845623.35</v>
       </c>
       <c r="G2" t="n">
-        <v>6009983790.23</v>
+        <v>3903323468.94</v>
       </c>
       <c r="H2" t="n">
-        <v>13602953149.6</v>
+        <v>10274552734.64</v>
       </c>
       <c r="I2" t="n">
-        <v>256801496.36</v>
+        <v>361300533.93</v>
       </c>
       <c r="J2" t="n">
-        <v>14606455619.02</v>
+        <v>11221560023.75</v>
       </c>
       <c r="K2" t="n">
-        <v>14606455619.02</v>
+        <v>11221560023.75</v>
       </c>
       <c r="L2" t="n">
-        <v>15006929048.41</v>
+        <v>11109688559.42</v>
       </c>
       <c r="M2" t="n">
-        <v>400473429.39</v>
+        <v>-111871464.33</v>
       </c>
       <c r="N2" t="n">
-        <v>14606455619.02</v>
+        <v>11221560023.75</v>
       </c>
       <c r="O2" t="n">
-        <v>7561485821.67</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>5227141020.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2540421521.7</v>
+      </c>
       <c r="Q2" t="n">
         <v>1233841000</v>
       </c>
@@ -1833,181 +1835,185 @@
         <v>1233841000</v>
       </c>
       <c r="S2" t="n">
-        <v>7891774311.86</v>
+        <v>7664257231.46</v>
       </c>
       <c r="T2" t="n">
-        <v>298237431.1</v>
+        <v>323613529.62</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>53436961.2</v>
+        <v>31146881.78</v>
       </c>
       <c r="X2" t="n">
-        <v>64861474.37</v>
+        <v>32872282.61</v>
       </c>
       <c r="Y2" t="n">
-        <v>179938995.53</v>
+        <v>259594365.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>179938995.53</v>
+        <v>259594365.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>7593536880.76</v>
+        <v>7340643701.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>121307453.93</v>
+        <v>100371095.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>91349168.33</v>
+        <v>146991768.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>76862500.83</v>
+        <v>101706168.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>14486667.5</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>45285599.6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>594173428.34</v>
+      </c>
       <c r="AG2" t="n">
-        <v>6719361718.71</v>
+        <v>6454297789.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>1217274272.29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
+        <v>981060223.8099999</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>49054970.83</v>
+        <v>66656385.64</v>
       </c>
       <c r="AK2" t="n">
-        <v>5453032475.59</v>
+        <v>5406581179.99</v>
       </c>
       <c r="AL2" t="n">
-        <v>22898703360.27</v>
+        <v>18773945790.88</v>
       </c>
       <c r="AM2" t="n">
-        <v>9295182689.280001</v>
+        <v>7529978620.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>11067468.46</v>
+        <v>791530359.26</v>
       </c>
       <c r="AO2" t="n">
-        <v>1016595.47</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>709616.75</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15260900.36</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>7215301.85</v>
+        <v>23931737.96</v>
       </c>
       <c r="AR2" t="n">
-        <v>4637306882.41</v>
+        <v>2986772869.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>4637306882.41</v>
+        <v>2986772869.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>806322100.7</v>
+        <v>757803876.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>806322100.7</v>
+        <v>757803876.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>76601687.11</v>
+        <v>82653580.43000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1003502469.42</v>
+        <v>947007289.11</v>
       </c>
       <c r="AX2" t="n">
-        <v>380849562.18</v>
+        <v>446435707.97</v>
       </c>
       <c r="AY2" t="n">
-        <v>622652907.24</v>
+        <v>500571581.14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2712957304.97</v>
+        <v>2519143332.94</v>
       </c>
       <c r="BA2" t="n">
-        <v>-1816570414.67</v>
+        <v>-1367546735.71</v>
       </c>
       <c r="BB2" t="n">
-        <v>4529527719.64</v>
+        <v>3886690068.65</v>
       </c>
       <c r="BC2" t="n">
-        <v>118668839.11</v>
+        <v>159346048.51</v>
       </c>
       <c r="BD2" t="n">
-        <v>220236037.74</v>
+        <v>192355595.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>493882860.68</v>
+        <v>442477369.77</v>
       </c>
       <c r="BF2" t="n">
-        <v>3696739982.11</v>
+        <v>3092511055.28</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>13603520670.99</v>
+        <v>11243967170.78</v>
       </c>
       <c r="BI2" t="n">
-        <v>296166.19</v>
+        <v>674571277.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>49263308.47</v>
+        <v>172294518.11</v>
       </c>
       <c r="BK2" t="n">
-        <v>40199746.06</v>
+        <v>1263751.95</v>
       </c>
       <c r="BL2" t="n">
-        <v>64815102</v>
+        <v>79323179.34999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>2422588723.48</v>
+        <v>2742158426.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>2226277844.97</v>
+        <v>2482172222.18</v>
       </c>
       <c r="BO2" t="n">
-        <v>167871078.11</v>
+        <v>202673827.36</v>
       </c>
       <c r="BP2" t="n">
-        <v>28439800.4</v>
+        <v>57312377.3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>333134476.76</v>
+        <v>241671462.97</v>
       </c>
       <c r="BR2" t="n">
-        <v>26874390.21</v>
+        <v>11355211.82</v>
       </c>
       <c r="BS2" t="n">
-        <v>1526810256.53</v>
+        <v>1555884147.93</v>
       </c>
       <c r="BT2" t="n">
-        <v>-862123401.0599999</v>
+        <v>-572499992.34</v>
       </c>
       <c r="BU2" t="n">
-        <v>2388933657.59</v>
+        <v>2128384140.27</v>
       </c>
       <c r="BV2" t="n">
-        <v>9139538501.290001</v>
+        <v>6441280223.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>60122.67</v>
+        <v>401250945.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>9139478378.620001</v>
-      </c>
-      <c r="BY2" t="inlineStr"/>
+        <v>6040029278.72</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>5995023900.96</v>
+      </c>
       <c r="BZ2" t="n">
-        <v>9139478378.620001</v>
+        <v>6040029278.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1233841000</v>
@@ -2016,42 +2022,44 @@
         <v>1233841000</v>
       </c>
       <c r="D3" t="n">
-        <v>372004849.38</v>
+        <v>453940250.63</v>
       </c>
       <c r="E3" t="n">
-        <v>12042040502.77</v>
+        <v>11427434141.15</v>
       </c>
       <c r="F3" t="n">
-        <v>13117247827.16</v>
+        <v>12537755729.56</v>
       </c>
       <c r="G3" t="n">
-        <v>6134458394.42</v>
+        <v>5207710274.58</v>
       </c>
       <c r="H3" t="n">
-        <v>12042040502.77</v>
+        <v>11427434141.15</v>
       </c>
       <c r="I3" t="n">
-        <v>325705165.57</v>
+        <v>406163944.7</v>
       </c>
       <c r="J3" t="n">
-        <v>13070948143.35</v>
+        <v>12489979423.63</v>
       </c>
       <c r="K3" t="n">
-        <v>13070948143.35</v>
+        <v>12489979423.63</v>
       </c>
       <c r="L3" t="n">
-        <v>13414156171.11</v>
+        <v>12662033360.06</v>
       </c>
       <c r="M3" t="n">
-        <v>343208027.76</v>
+        <v>172053936.43</v>
       </c>
       <c r="N3" t="n">
-        <v>13070948143.35</v>
+        <v>12489979423.63</v>
       </c>
       <c r="O3" t="n">
-        <v>6881030888.86</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>6083770928.98</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2540421521.7</v>
+      </c>
       <c r="Q3" t="n">
         <v>1233841000</v>
       </c>
@@ -2059,183 +2067,189 @@
         <v>1233841000</v>
       </c>
       <c r="S3" t="n">
-        <v>8373407203.21</v>
+        <v>7989354199.3</v>
       </c>
       <c r="T3" t="n">
-        <v>499231350.93</v>
+        <v>446900033.07</v>
       </c>
       <c r="U3" t="n">
-        <v>30581649.9</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>33142176.77</v>
+      </c>
+      <c r="V3" t="n">
+        <v>33142176.77</v>
+      </c>
       <c r="W3" t="n">
-        <v>20083863.8</v>
+        <v>25359348.84</v>
       </c>
       <c r="X3" t="n">
-        <v>217635807.37</v>
+        <v>73867204.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>230930029.86</v>
+        <v>314531302.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>230930029.86</v>
+        <v>314531302.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>7874175852.28</v>
+        <v>7542454166.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>123909365.77</v>
+        <v>113079270.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>141074819.52</v>
+        <v>139408947.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>94775135.70999999</v>
+        <v>91632641.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>46299683.81</v>
+        <v>47776305.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>795130708.6799999</v>
+        <v>704546289.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>6905948023.87</v>
+        <v>6608610329.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1137215433.22</v>
+        <v>1108921249.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>222091380</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>76583113.89</v>
+        <v>75289417.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>5470058096.76</v>
+        <v>5424399662.93</v>
       </c>
       <c r="AL3" t="n">
-        <v>21787563374.32</v>
+        <v>20651387559.36</v>
       </c>
       <c r="AM3" t="n">
-        <v>7778929127.62</v>
+        <v>7901223118.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>13497664.54</v>
+        <v>15808962.69</v>
       </c>
       <c r="AO3" t="n">
-        <v>27944.42</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>351233.02</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>44357505.3</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>50401253.62</v>
+        <v>23891140.32</v>
       </c>
       <c r="AR3" t="n">
-        <v>2973306848.56</v>
+        <v>2918952599.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>2973306848.56</v>
+        <v>2918952599.27</v>
       </c>
       <c r="AT3" t="n">
-        <v>771481018.72</v>
+        <v>748393704.39</v>
       </c>
       <c r="AU3" t="n">
-        <v>771481018.72</v>
+        <v>748393704.39</v>
       </c>
       <c r="AV3" t="n">
-        <v>94146451.73</v>
+        <v>95997370.92</v>
       </c>
       <c r="AW3" t="n">
-        <v>1028907640.58</v>
+        <v>1062545282.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>406254733.34</v>
+        <v>439892375.24</v>
       </c>
       <c r="AY3" t="n">
         <v>622652907.24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2803927274.42</v>
+        <v>2931698165.66</v>
       </c>
       <c r="BA3" t="n">
-        <v>-1721572997.9</v>
+        <v>-1532683282.74</v>
       </c>
       <c r="BB3" t="n">
-        <v>4525500272.32</v>
+        <v>4464381448.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>124099099.77</v>
+        <v>99021688.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>225112096.92</v>
+        <v>224796633.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>480573559.79</v>
+        <v>468882886.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>3695715515.84</v>
+        <v>3671680239.36</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>14008634246.7</v>
-      </c>
-      <c r="BI3" t="inlineStr"/>
+        <v>12750164440.81</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.01</v>
+      </c>
       <c r="BJ3" t="n">
-        <v>69763811.83</v>
+        <v>117238899.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>39321000.73</v>
+        <v>39715877.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>55483678.87</v>
+        <v>78587315.95</v>
       </c>
       <c r="BM3" t="n">
-        <v>2641169798.03</v>
+        <v>2572840225.77</v>
       </c>
       <c r="BN3" t="n">
-        <v>2446015695.67</v>
+        <v>2364482639.98</v>
       </c>
       <c r="BO3" t="n">
-        <v>135593328.09</v>
+        <v>156205462.21</v>
       </c>
       <c r="BP3" t="n">
-        <v>59560774.27</v>
+        <v>52152123.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>187781608.11</v>
+        <v>213079812.29</v>
       </c>
       <c r="BR3" t="n">
-        <v>8122102.43</v>
+        <v>11802113.73</v>
       </c>
       <c r="BS3" t="n">
-        <v>1477171063.02</v>
+        <v>1697878791.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>-824907918.37</v>
+        <v>-734075891.09</v>
       </c>
       <c r="BU3" t="n">
-        <v>2302078981.39</v>
+        <v>2431954682.56</v>
       </c>
       <c r="BV3" t="n">
-        <v>9529821183.68</v>
+        <v>8019021404.62</v>
       </c>
       <c r="BW3" t="n">
-        <v>451478358.89</v>
+        <v>256936775.34</v>
       </c>
       <c r="BX3" t="n">
-        <v>9078342824.790001</v>
+        <v>7762084629.28</v>
       </c>
       <c r="BY3" t="n">
-        <v>9069443251.83</v>
+        <v>7760122171.46</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9078342824.790001</v>
+        <v>7762084629.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1233841000</v>
@@ -2244,44 +2258,42 @@
         <v>1233841000</v>
       </c>
       <c r="D4" t="n">
-        <v>453940250.63</v>
+        <v>372004849.38</v>
       </c>
       <c r="E4" t="n">
-        <v>11427434141.15</v>
+        <v>12042040502.77</v>
       </c>
       <c r="F4" t="n">
-        <v>12537755729.56</v>
+        <v>13117247827.16</v>
       </c>
       <c r="G4" t="n">
-        <v>5207710274.58</v>
+        <v>6134458394.42</v>
       </c>
       <c r="H4" t="n">
-        <v>11427434141.15</v>
+        <v>12042040502.77</v>
       </c>
       <c r="I4" t="n">
-        <v>406163944.7</v>
+        <v>325705165.57</v>
       </c>
       <c r="J4" t="n">
-        <v>12489979423.63</v>
+        <v>13070948143.35</v>
       </c>
       <c r="K4" t="n">
-        <v>12489979423.63</v>
+        <v>13070948143.35</v>
       </c>
       <c r="L4" t="n">
-        <v>12662033360.06</v>
+        <v>13414156171.11</v>
       </c>
       <c r="M4" t="n">
-        <v>172053936.43</v>
+        <v>343208027.76</v>
       </c>
       <c r="N4" t="n">
-        <v>12489979423.63</v>
+        <v>13070948143.35</v>
       </c>
       <c r="O4" t="n">
-        <v>6083770928.98</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2540421521.7</v>
-      </c>
+        <v>6881030888.86</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>1233841000</v>
       </c>
@@ -2289,189 +2301,183 @@
         <v>1233841000</v>
       </c>
       <c r="S4" t="n">
-        <v>7989354199.3</v>
+        <v>8373407203.21</v>
       </c>
       <c r="T4" t="n">
-        <v>446900033.07</v>
+        <v>499231350.93</v>
       </c>
       <c r="U4" t="n">
-        <v>33142176.77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>33142176.77</v>
-      </c>
+        <v>30581649.9</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>25359348.84</v>
+        <v>20083863.8</v>
       </c>
       <c r="X4" t="n">
-        <v>73867204.7</v>
+        <v>217635807.37</v>
       </c>
       <c r="Y4" t="n">
-        <v>314531302.76</v>
+        <v>230930029.86</v>
       </c>
       <c r="Z4" t="n">
-        <v>314531302.76</v>
+        <v>230930029.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>7542454166.23</v>
+        <v>7874175852.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>113079270.81</v>
+        <v>123909365.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>139408947.87</v>
+        <v>141074819.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>91632641.94</v>
+        <v>94775135.70999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>47776305.93</v>
+        <v>46299683.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>704546289.83</v>
+        <v>795130708.6799999</v>
       </c>
       <c r="AG4" t="n">
-        <v>6608610329.38</v>
+        <v>6905948023.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>1108921249.09</v>
+        <v>1137215433.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>222091380</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75289417.36</v>
+        <v>76583113.89</v>
       </c>
       <c r="AK4" t="n">
-        <v>5424399662.93</v>
+        <v>5470058096.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>20651387559.36</v>
+        <v>21787563374.32</v>
       </c>
       <c r="AM4" t="n">
-        <v>7901223118.55</v>
+        <v>7778929127.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>15808962.69</v>
+        <v>13497664.54</v>
       </c>
       <c r="AO4" t="n">
-        <v>351233.02</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>44357505.3</v>
-      </c>
+        <v>27944.42</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>23891140.32</v>
+        <v>50401253.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>2918952599.27</v>
+        <v>2973306848.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>2918952599.27</v>
+        <v>2973306848.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>748393704.39</v>
+        <v>771481018.72</v>
       </c>
       <c r="AU4" t="n">
-        <v>748393704.39</v>
+        <v>771481018.72</v>
       </c>
       <c r="AV4" t="n">
-        <v>95997370.92</v>
+        <v>94146451.73</v>
       </c>
       <c r="AW4" t="n">
-        <v>1062545282.48</v>
+        <v>1028907640.58</v>
       </c>
       <c r="AX4" t="n">
-        <v>439892375.24</v>
+        <v>406254733.34</v>
       </c>
       <c r="AY4" t="n">
         <v>622652907.24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2931698165.66</v>
+        <v>2803927274.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1532683282.74</v>
+        <v>-1721572997.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>4464381448.4</v>
+        <v>4525500272.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>99021688.55</v>
+        <v>124099099.77</v>
       </c>
       <c r="BD4" t="n">
-        <v>224796633.75</v>
+        <v>225112096.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>468882886.74</v>
+        <v>480573559.79</v>
       </c>
       <c r="BF4" t="n">
-        <v>3671680239.36</v>
+        <v>3695715515.84</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>12750164440.81</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.01</v>
-      </c>
+        <v>14008634246.7</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>117238899.64</v>
+        <v>69763811.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>39715877.33</v>
+        <v>39321000.73</v>
       </c>
       <c r="BL4" t="n">
-        <v>78587315.95</v>
+        <v>55483678.87</v>
       </c>
       <c r="BM4" t="n">
-        <v>2572840225.77</v>
+        <v>2641169798.03</v>
       </c>
       <c r="BN4" t="n">
-        <v>2364482639.98</v>
+        <v>2446015695.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>156205462.21</v>
+        <v>135593328.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>52152123.58</v>
+        <v>59560774.27</v>
       </c>
       <c r="BQ4" t="n">
-        <v>213079812.29</v>
+        <v>187781608.11</v>
       </c>
       <c r="BR4" t="n">
-        <v>11802113.73</v>
+        <v>8122102.43</v>
       </c>
       <c r="BS4" t="n">
-        <v>1697878791.47</v>
+        <v>1477171063.02</v>
       </c>
       <c r="BT4" t="n">
-        <v>-734075891.09</v>
+        <v>-824907918.37</v>
       </c>
       <c r="BU4" t="n">
-        <v>2431954682.56</v>
+        <v>2302078981.39</v>
       </c>
       <c r="BV4" t="n">
-        <v>8019021404.62</v>
+        <v>9529821183.68</v>
       </c>
       <c r="BW4" t="n">
-        <v>256936775.34</v>
+        <v>451478358.89</v>
       </c>
       <c r="BX4" t="n">
-        <v>7762084629.28</v>
+        <v>9078342824.790001</v>
       </c>
       <c r="BY4" t="n">
-        <v>7760122171.46</v>
+        <v>9069443251.83</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7762084629.28</v>
+        <v>9078342824.790001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1233841000</v>
@@ -2480,44 +2486,42 @@
         <v>1233841000</v>
       </c>
       <c r="D5" t="n">
-        <v>406586133.53</v>
+        <v>271288163.86</v>
       </c>
       <c r="E5" t="n">
-        <v>10274552734.64</v>
+        <v>13602953149.6</v>
       </c>
       <c r="F5" t="n">
-        <v>11266845623.35</v>
+        <v>14620942286.52</v>
       </c>
       <c r="G5" t="n">
-        <v>3903323468.94</v>
+        <v>6009983790.23</v>
       </c>
       <c r="H5" t="n">
-        <v>10274552734.64</v>
+        <v>13602953149.6</v>
       </c>
       <c r="I5" t="n">
-        <v>361300533.93</v>
+        <v>256801496.36</v>
       </c>
       <c r="J5" t="n">
-        <v>11221560023.75</v>
+        <v>14606455619.02</v>
       </c>
       <c r="K5" t="n">
-        <v>11221560023.75</v>
+        <v>14606455619.02</v>
       </c>
       <c r="L5" t="n">
-        <v>11109688559.42</v>
+        <v>15006929048.41</v>
       </c>
       <c r="M5" t="n">
-        <v>-111871464.33</v>
+        <v>400473429.39</v>
       </c>
       <c r="N5" t="n">
-        <v>11221560023.75</v>
+        <v>14606455619.02</v>
       </c>
       <c r="O5" t="n">
-        <v>5227141020.57</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2540421521.7</v>
-      </c>
+        <v>7561485821.67</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>1233841000</v>
       </c>
@@ -2525,180 +2529,176 @@
         <v>1233841000</v>
       </c>
       <c r="S5" t="n">
-        <v>7664257231.46</v>
+        <v>7891774311.86</v>
       </c>
       <c r="T5" t="n">
-        <v>323613529.62</v>
+        <v>298237431.1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>31146881.78</v>
+        <v>53436961.2</v>
       </c>
       <c r="X5" t="n">
-        <v>32872282.61</v>
+        <v>64861474.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>259594365.23</v>
+        <v>179938995.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>259594365.23</v>
+        <v>179938995.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>7340643701.84</v>
+        <v>7593536880.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>100371095.77</v>
+        <v>121307453.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>146991768.3</v>
+        <v>91349168.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>101706168.7</v>
+        <v>76862500.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>45285599.6</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>594173428.34</v>
-      </c>
+        <v>14486667.5</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>6454297789.44</v>
+        <v>6719361718.71</v>
       </c>
       <c r="AH5" t="n">
-        <v>981060223.8099999</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>1217274272.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>66656385.64</v>
+        <v>49054970.83</v>
       </c>
       <c r="AK5" t="n">
-        <v>5406581179.99</v>
+        <v>5453032475.59</v>
       </c>
       <c r="AL5" t="n">
-        <v>18773945790.88</v>
+        <v>22898703360.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>7529978620.1</v>
+        <v>9295182689.280001</v>
       </c>
       <c r="AN5" t="n">
-        <v>791530359.26</v>
+        <v>11067468.46</v>
       </c>
       <c r="AO5" t="n">
-        <v>709616.75</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15260900.36</v>
-      </c>
+        <v>1016595.47</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>23931737.96</v>
+        <v>7215301.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>2986772869.8</v>
+        <v>4637306882.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>2986772869.8</v>
+        <v>4637306882.41</v>
       </c>
       <c r="AT5" t="n">
-        <v>757803876.08</v>
+        <v>806322100.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>757803876.08</v>
+        <v>806322100.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>82653580.43000001</v>
+        <v>76601687.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>947007289.11</v>
+        <v>1003502469.42</v>
       </c>
       <c r="AX5" t="n">
-        <v>446435707.97</v>
+        <v>380849562.18</v>
       </c>
       <c r="AY5" t="n">
-        <v>500571581.14</v>
+        <v>622652907.24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2519143332.94</v>
+        <v>2712957304.97</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1367546735.71</v>
+        <v>-1816570414.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>3886690068.65</v>
+        <v>4529527719.64</v>
       </c>
       <c r="BC5" t="n">
-        <v>159346048.51</v>
+        <v>118668839.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>192355595.09</v>
+        <v>220236037.74</v>
       </c>
       <c r="BE5" t="n">
-        <v>442477369.77</v>
+        <v>493882860.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>3092511055.28</v>
+        <v>3696739982.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>11243967170.78</v>
+        <v>13603520670.99</v>
       </c>
       <c r="BI5" t="n">
-        <v>674571277.55</v>
+        <v>296166.19</v>
       </c>
       <c r="BJ5" t="n">
-        <v>172294518.11</v>
+        <v>49263308.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>1263751.95</v>
+        <v>40199746.06</v>
       </c>
       <c r="BL5" t="n">
-        <v>79323179.34999999</v>
+        <v>64815102</v>
       </c>
       <c r="BM5" t="n">
-        <v>2742158426.84</v>
+        <v>2422588723.48</v>
       </c>
       <c r="BN5" t="n">
-        <v>2482172222.18</v>
+        <v>2226277844.97</v>
       </c>
       <c r="BO5" t="n">
-        <v>202673827.36</v>
+        <v>167871078.11</v>
       </c>
       <c r="BP5" t="n">
-        <v>57312377.3</v>
+        <v>28439800.4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>241671462.97</v>
+        <v>333134476.76</v>
       </c>
       <c r="BR5" t="n">
-        <v>11355211.82</v>
+        <v>26874390.21</v>
       </c>
       <c r="BS5" t="n">
-        <v>1555884147.93</v>
+        <v>1526810256.53</v>
       </c>
       <c r="BT5" t="n">
-        <v>-572499992.34</v>
+        <v>-862123401.0599999</v>
       </c>
       <c r="BU5" t="n">
-        <v>2128384140.27</v>
+        <v>2388933657.59</v>
       </c>
       <c r="BV5" t="n">
-        <v>6441280223.76</v>
+        <v>9139538501.290001</v>
       </c>
       <c r="BW5" t="n">
-        <v>401250945.04</v>
+        <v>60122.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>6040029278.72</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>5995023900.96</v>
-      </c>
+        <v>9139478378.620001</v>
+      </c>
+      <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>6040029278.72</v>
+        <v>9139478378.620001</v>
       </c>
     </row>
   </sheetData>
@@ -2984,41 +2984,41 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1621281994.16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-10000000</v>
-      </c>
+        <v>1773579689.56</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-151196837.47</v>
+        <v>-273749887.65</v>
       </c>
       <c r="F2" t="n">
-        <v>8962582856.290001</v>
+        <v>5997769686.81</v>
       </c>
       <c r="G2" t="n">
-        <v>9078342824.790001</v>
+        <v>5740841068.18</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-115759968.5</v>
+        <v>256928618.63</v>
       </c>
       <c r="J2" t="n">
-        <v>-1065293099.26</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>-511795258.22</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-128772750.81</v>
+      </c>
       <c r="L2" t="n">
-        <v>-950884516.13</v>
+        <v>-383022507.41</v>
       </c>
       <c r="M2" t="n">
-        <v>-950884516.13</v>
+        <v>-383022507.41</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -3026,473 +3026,477 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>-10000000</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>-822945700.87</v>
+        <v>-1278605700.36</v>
       </c>
       <c r="U2" t="n">
-        <v>-490830737.7</v>
+        <v>73149634.02</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-183313053.38</v>
+        <v>-1081952584.94</v>
       </c>
       <c r="X2" t="n">
-        <v>28450610.87</v>
+        <v>350201840.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>-211763664.25</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>-1432154425.63</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-148801909.79</v>
+        <v>-269802749.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>2394927.68</v>
+        <v>3947138.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>-151196837.47</v>
+        <v>-273749887.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>1772478831.63</v>
+        <v>2047329577.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>-11702113.99</v>
+        <v>444893219.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>91529031.73999999</v>
+        <v>4340194.93</v>
       </c>
       <c r="AH2" t="n">
-        <v>-45960613.96</v>
+        <v>1053936935.72</v>
       </c>
       <c r="AI2" t="n">
-        <v>172532609.23</v>
+        <v>-659932161.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-229803141</v>
+        <v>46548250.41</v>
       </c>
       <c r="AK2" t="n">
-        <v>-14310155.83</v>
+        <v>14012337.31</v>
       </c>
       <c r="AL2" t="n">
-        <v>294039254.73</v>
+        <v>290421944.43</v>
       </c>
       <c r="AM2" t="n">
-        <v>43311771.71</v>
+        <v>33997994.29</v>
       </c>
       <c r="AN2" t="n">
-        <v>250727483.02</v>
+        <v>256423950.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>-120362320.86</v>
+        <v>-141380824.26</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1655050.26</v>
+        <v>-2015713.48</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>1603661673.85</v>
+        <v>1303281261.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>1772478831.63</v>
+        <v>2047329577.21</v>
       </c>
       <c r="AT2" t="n">
-        <v>-289009758.36</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>-131150133.87</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>78056426.08</v>
+      </c>
       <c r="AV2" t="n">
-        <v>-11272023281.62</v>
+        <v>-9152017602.870001</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1301356224.42</v>
+        <v>-1108782003.37</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1838151893.23</v>
+        <v>-1331002015.79</v>
       </c>
       <c r="AY2" t="n">
-        <v>-8132515163.97</v>
+        <v>-6712233583.71</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13333511871.61</v>
+        <v>11252440887.87</v>
       </c>
       <c r="BA2" t="n">
-        <v>393903480.51</v>
+        <v>134195335.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>12939608391.1</v>
+        <v>11118245552.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2172537081.81</v>
+        <v>1807671460.22</v>
       </c>
       <c r="C3" t="n">
-        <v>-18000000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10000000</v>
+        <v>18000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-180491129.51</v>
+        <v>-216709664.4</v>
       </c>
       <c r="F3" t="n">
-        <v>9078342824.790001</v>
+        <v>7762084629.28</v>
       </c>
       <c r="G3" t="n">
-        <v>7762084629.28</v>
+        <v>5997769686.81</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1316258195.51</v>
+        <v>1764314942.47</v>
       </c>
       <c r="J3" t="n">
-        <v>-575819199.8200001</v>
+        <v>-492510346.28</v>
       </c>
       <c r="K3" t="n">
-        <v>-34768400</v>
+        <v>-115095378.01</v>
       </c>
       <c r="L3" t="n">
-        <v>-420820187.6</v>
+        <v>-395414968.27</v>
       </c>
       <c r="M3" t="n">
-        <v>-420820187.6</v>
+        <v>-395414968.27</v>
       </c>
       <c r="N3" t="n">
-        <v>-8000000</v>
+        <v>18000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-8000000</v>
+        <v>18000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-18000000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>18000000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18000000</v>
+      </c>
       <c r="T3" t="n">
-        <v>-460950815.99</v>
+        <v>232444164.13</v>
       </c>
       <c r="U3" t="n">
-        <v>94654647.56</v>
+        <v>100937967.71</v>
       </c>
       <c r="V3" t="n">
-        <v>22076126.01</v>
+        <v>8062499.89</v>
       </c>
       <c r="W3" t="n">
-        <v>-403285479.47</v>
+        <v>370283115.66</v>
       </c>
       <c r="X3" t="n">
-        <v>420126653.55</v>
+        <v>962087592.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>-823412133.02</v>
+        <v>-591804476.98</v>
       </c>
       <c r="Z3" t="n">
+        <v>-71730019.83</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-71730019.83</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-175109399.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>41600265.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-216709664.4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2024381124.62</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>190541293.14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-21724351.12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>124775757.67</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>131587617.78</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-44097731.19</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8868430.220000001</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>268112504.44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>41283424.49</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>226829079.95</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-3992744.72</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-40693328.27</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-174396110.09</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6095019.42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-180491129.51</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2353028211.32</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>273968953.94</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-83737290.69</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>325548133.04</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-138668646.11</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>170826757.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>11799968.57</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>286076643.8</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>42669541.74</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>243407102.06</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>19767809.92</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-2176929.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>54160591.53</v>
-      </c>
       <c r="AR3" t="n">
-        <v>1628350305.31</v>
+        <v>1391235128.21</v>
       </c>
       <c r="AS3" t="n">
-        <v>2353028211.32</v>
+        <v>2024381124.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>-113490136.5</v>
+        <v>-42844205.72</v>
       </c>
       <c r="AU3" t="n">
-        <v>221637628.52</v>
+        <v>130700513.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>-10680317458.73</v>
+        <v>-9481678731.57</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1194928721.63</v>
+        <v>-1004575935.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1715047781.2</v>
+        <v>-1476143204.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>-7770340955.9</v>
+        <v>-7000959591.85</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13146835806.55</v>
+        <v>11418203548.16</v>
       </c>
       <c r="BA3" t="n">
-        <v>314280677.37</v>
+        <v>145730797.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>12832555129.18</v>
+        <v>11272472750.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1807671460.22</v>
+        <v>2172537081.81</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-18000000</v>
       </c>
       <c r="D4" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-216709664.4</v>
+        <v>-180491129.51</v>
       </c>
       <c r="F4" t="n">
+        <v>9078342824.790001</v>
+      </c>
+      <c r="G4" t="n">
         <v>7762084629.28</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5997769686.81</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1764314942.47</v>
+        <v>1316258195.51</v>
       </c>
       <c r="J4" t="n">
-        <v>-492510346.28</v>
+        <v>-575819199.8200001</v>
       </c>
       <c r="K4" t="n">
-        <v>-115095378.01</v>
+        <v>-34768400</v>
       </c>
       <c r="L4" t="n">
-        <v>-395414968.27</v>
+        <v>-420820187.6</v>
       </c>
       <c r="M4" t="n">
-        <v>-395414968.27</v>
+        <v>-420820187.6</v>
       </c>
       <c r="N4" t="n">
-        <v>18000000</v>
+        <v>-8000000</v>
       </c>
       <c r="O4" t="n">
-        <v>18000000</v>
+        <v>-8000000</v>
       </c>
       <c r="P4" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>-460950815.99</v>
+      </c>
+      <c r="U4" t="n">
+        <v>94654647.56</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22076126.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-403285479.47</v>
+      </c>
+      <c r="X4" t="n">
+        <v>420126653.55</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-823412133.02</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>232444164.13</v>
-      </c>
-      <c r="U4" t="n">
-        <v>100937967.71</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8062499.89</v>
-      </c>
-      <c r="W4" t="n">
-        <v>370283115.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>962087592.64</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-591804476.98</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-71730019.83</v>
-      </c>
       <c r="AA4" t="n">
-        <v>-71730019.83</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-175109399.3</v>
+        <v>-174396110.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>41600265.1</v>
+        <v>6095019.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>-216709664.4</v>
+        <v>-180491129.51</v>
       </c>
       <c r="AE4" t="n">
-        <v>2024381124.62</v>
+        <v>2353028211.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>190541293.14</v>
+        <v>273968953.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>-21724351.12</v>
+        <v>-83737290.69</v>
       </c>
       <c r="AH4" t="n">
-        <v>124775757.67</v>
+        <v>325548133.04</v>
       </c>
       <c r="AI4" t="n">
-        <v>131587617.78</v>
+        <v>-138668646.11</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-44097731.19</v>
+        <v>170826757.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>8868430.220000001</v>
+        <v>11799968.57</v>
       </c>
       <c r="AL4" t="n">
-        <v>268112504.44</v>
+        <v>286076643.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>41283424.49</v>
+        <v>42669541.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>226829079.95</v>
+        <v>243407102.06</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3992744.72</v>
+        <v>19767809.92</v>
       </c>
       <c r="AP4" t="n">
-        <v>-40693328.27</v>
+        <v>-2176929.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>54160591.53</v>
       </c>
       <c r="AR4" t="n">
-        <v>1391235128.21</v>
+        <v>1628350305.31</v>
       </c>
       <c r="AS4" t="n">
-        <v>2024381124.62</v>
+        <v>2353028211.32</v>
       </c>
       <c r="AT4" t="n">
-        <v>-42844205.72</v>
+        <v>-113490136.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>130700513.75</v>
+        <v>221637628.52</v>
       </c>
       <c r="AV4" t="n">
-        <v>-9481678731.57</v>
+        <v>-10680317458.73</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1004575935.48</v>
+        <v>-1194928721.63</v>
       </c>
       <c r="AX4" t="n">
-        <v>-1476143204.24</v>
+        <v>-1715047781.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>-7000959591.85</v>
+        <v>-7770340955.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11418203548.16</v>
+        <v>13146835806.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>145730797.62</v>
+        <v>314280677.37</v>
       </c>
       <c r="BB4" t="n">
-        <v>11272472750.54</v>
+        <v>12832555129.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1773579689.56</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>1621281994.16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-10000000</v>
+      </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-273749887.65</v>
+        <v>-151196837.47</v>
       </c>
       <c r="F5" t="n">
-        <v>5997769686.81</v>
+        <v>8962582856.290001</v>
       </c>
       <c r="G5" t="n">
-        <v>5740841068.18</v>
+        <v>9078342824.790001</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>256928618.63</v>
+        <v>-115759968.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-511795258.22</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-128772750.81</v>
-      </c>
+        <v>-1065293099.26</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-383022507.41</v>
+        <v>-950884516.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-383022507.41</v>
+        <v>-950884516.13</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3500,114 +3504,110 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>-10000000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-1278605700.36</v>
+        <v>-822945700.87</v>
       </c>
       <c r="U5" t="n">
-        <v>73149634.02</v>
+        <v>-490830737.7</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1081952584.94</v>
+        <v>-183313053.38</v>
       </c>
       <c r="X5" t="n">
-        <v>350201840.69</v>
+        <v>28450610.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1432154425.63</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>-211763664.25</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-269802749.44</v>
+        <v>-148801909.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>3947138.21</v>
+        <v>2394927.68</v>
       </c>
       <c r="AD5" t="n">
-        <v>-273749887.65</v>
+        <v>-151196837.47</v>
       </c>
       <c r="AE5" t="n">
-        <v>2047329577.21</v>
+        <v>1772478831.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>444893219.36</v>
+        <v>-11702113.99</v>
       </c>
       <c r="AG5" t="n">
-        <v>4340194.93</v>
+        <v>91529031.73999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>1053936935.72</v>
+        <v>-45960613.96</v>
       </c>
       <c r="AI5" t="n">
-        <v>-659932161.7</v>
+        <v>172532609.23</v>
       </c>
       <c r="AJ5" t="n">
-        <v>46548250.41</v>
+        <v>-229803141</v>
       </c>
       <c r="AK5" t="n">
-        <v>14012337.31</v>
+        <v>-14310155.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>290421944.43</v>
+        <v>294039254.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>33997994.29</v>
+        <v>43311771.71</v>
       </c>
       <c r="AN5" t="n">
-        <v>256423950.14</v>
+        <v>250727483.02</v>
       </c>
       <c r="AO5" t="n">
-        <v>-141380824.26</v>
+        <v>-120362320.86</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2015713.48</v>
+        <v>-1655050.26</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>1303281261.88</v>
+        <v>1603661673.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>2047329577.21</v>
+        <v>1772478831.63</v>
       </c>
       <c r="AT5" t="n">
-        <v>-131150133.87</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>78056426.08</v>
-      </c>
+        <v>-289009758.36</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-9152017602.870001</v>
+        <v>-11272023281.62</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1108782003.37</v>
+        <v>-1301356224.42</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1331002015.79</v>
+        <v>-1838151893.23</v>
       </c>
       <c r="AY5" t="n">
-        <v>-6712233583.71</v>
+        <v>-8132515163.97</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11252440887.87</v>
+        <v>13333511871.61</v>
       </c>
       <c r="BA5" t="n">
-        <v>134195335.42</v>
+        <v>393903480.51</v>
       </c>
       <c r="BB5" t="n">
-        <v>11118245552.45</v>
+        <v>12939608391.1</v>
       </c>
     </row>
   </sheetData>
@@ -4187,167 +4187,167 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Qing  Zhou', 'age': 55, 'title': 'Executive Chairman', 'yearBorn': 1970, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Longzhang  Liu', 'age': 58, 'title': 'Executive Vice Chairman', 'yearBorn': 1967, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong Ping  Xu', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Miao  Yang', 'age': 43, 'title': 'Board Secretary', 'yearBorn': 1982, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Wang', 'age': 55, 'title': 'Deputy General Manager', 'yearBorn': 1970, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiaofeng  Ma', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Zou', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei  Hu', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bo  Hu', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kun  Li', 'age': 54, 'title': 'GM &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2014, 'totalPay': 56749, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Qing  Zhou', 'age': 55, 'title': 'Executive Chairman', 'yearBorn': 1970, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Longzhang  Liu', 'age': 58, 'title': 'Executive Vice Chairman', 'yearBorn': 1967, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong Ping  Xu', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Miao  Yang', 'age': 43, 'title': 'Board Secretary', 'yearBorn': 1982, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Wang', 'age': 55, 'title': 'Deputy General Manager', 'yearBorn': 1970, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiaofeng  Ma', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Zou', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei  Hu', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bo  Hu', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kun  Li', 'age': 54, 'title': 'GM &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2014, 'totalPay': 56718, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4455,34 +4455,34 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>9.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>9.69</v>
+        <v>8.82</v>
       </c>
       <c r="X2" t="n">
-        <v>9.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.69</v>
+        <v>8.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="AD2" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.11</v>
+        <v>7.74</v>
       </c>
       <c r="AF2" t="n">
         <v>1780012800</v>
@@ -4494,40 +4494,40 @@
         <v>6.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.5918365</v>
+        <v>6.0544214</v>
       </c>
       <c r="AK2" t="n">
-        <v>958000</v>
+        <v>966000</v>
       </c>
       <c r="AL2" t="n">
-        <v>958000</v>
+        <v>966000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1315759</v>
+        <v>1329678</v>
       </c>
       <c r="AN2" t="n">
-        <v>1845210</v>
+        <v>885559</v>
       </c>
       <c r="AO2" t="n">
-        <v>1845210</v>
+        <v>885559</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.630000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.640000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="AR2" t="n">
-        <v>11955918848</v>
+        <v>10981184512</v>
       </c>
       <c r="AS2" t="n">
-        <v>16280312390</v>
+        <v>14569473522</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.44</v>
+        <v>8.73</v>
       </c>
       <c r="AU2" t="n">
         <v>12.4</v>
@@ -4539,19 +4539,19 @@
         <v>0.98</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.0194694</v>
+        <v>0.9363547</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.3506</v>
+        <v>10.1788</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.61055</v>
+        <v>10.46345</v>
       </c>
       <c r="BA2" t="n">
         <v>0.61</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.06321243999999999</v>
+        <v>0.06747787399999999</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>4217391360</v>
+        <v>3242657024</v>
       </c>
       <c r="BF2" t="n">
         <v>0.13351</v>
@@ -4577,16 +4577,16 @@
         <v>0.35054</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.14524001</v>
+        <v>0.14403</v>
       </c>
       <c r="BK2" t="n">
         <v>1233841000</v>
       </c>
       <c r="BL2" t="n">
-        <v>14.601851</v>
+        <v>14.594103</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.66361445</v>
+        <v>0.6098353</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4607,16 +4607,16 @@
         <v>1.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.36</v>
+        <v>0.276</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.23</v>
+        <v>2.484</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.13530463</v>
+        <v>-0.18850988</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.481034</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>9.69</v>
+        <v>8.9</v>
       </c>
       <c r="CB2" t="n">
         <v>13</v>
@@ -4749,124 +4749,124 @@
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
+          <t>finmb_28706226</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-1.2788</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.12563367</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-1.5634508</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.1494202</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>finmb_28706226</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
+      <c r="DW2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-1.5486764</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>XINHUA WINSHARE</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>XINHUA WINSHARE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.66060066</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.06382245</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.92055035</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.086758025</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DZ2" t="b">
+      <c r="EB2" t="n">
+        <v>1180488600000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.14000034</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>8.73 - 8.93</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>1329678</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.17000008</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.01947309</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>8.73 - 12.4</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.28225806</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-18.850988</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
         <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.41450736</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1180488600000</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.03999996</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>9.62 - 9.78</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1315759</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.026483051</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>9.44 - 12.4</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.2185484</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-13.530463</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1.47</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
